--- a/2022 data/excel_outputs/396_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/396_boothwise_data.xlsx
@@ -14,11 +14,92 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="479">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="506">
   <si>
     <t>AC 396 Booth-wise Data</t>
   </si>
   <si>
+    <t>Unnamed: 1</t>
+  </si>
+  <si>
+    <t>Unnamed: 2</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>Unnamed: 6</t>
+  </si>
+  <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Unnamed: 9</t>
+  </si>
+  <si>
+    <t>Unnamed: 10</t>
+  </si>
+  <si>
+    <t>Unnamed: 11</t>
+  </si>
+  <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
+    <t>Unnamed: 13</t>
+  </si>
+  <si>
+    <t>Unnamed: 14</t>
+  </si>
+  <si>
+    <t>Unnamed: 15</t>
+  </si>
+  <si>
+    <t>Unnamed: 16</t>
+  </si>
+  <si>
+    <t>Unnamed: 17</t>
+  </si>
+  <si>
+    <t>Unnamed: 18</t>
+  </si>
+  <si>
+    <t>Unnamed: 19</t>
+  </si>
+  <si>
+    <t>Unnamed: 20</t>
+  </si>
+  <si>
+    <t>Unnamed: 21</t>
+  </si>
+  <si>
+    <t>Unnamed: 22</t>
+  </si>
+  <si>
+    <t>Unnamed: 23</t>
+  </si>
+  <si>
+    <t>Unnamed: 24</t>
+  </si>
+  <si>
+    <t>Unnamed: 25</t>
+  </si>
+  <si>
+    <t>Unnamed: 26</t>
+  </si>
+  <si>
+    <t>Unnamed: 27</t>
+  </si>
+  <si>
     <t>BOOTH ID</t>
   </si>
   <si>
@@ -907,10 +988,10 @@
     <t>NAGAR PALIKA KARYALAYA KAR V0, LALDIGGI ROOM NO-2</t>
   </si>
   <si>
-    <t>NAGAR PALIKA KARYALAYA KAR V0, LALDIGGI ■■■■ ■■0-3</t>
-  </si>
-  <si>
-    <t>NAGAR PALIKA KARYALAYA KAR V0, LALDIGGI ■■■■ ■■0-4</t>
+    <t>BOOTH 295</t>
+  </si>
+  <si>
+    <t>BOOTH 296</t>
   </si>
   <si>
     <t>ISHWARCHAND VIDYASAGAR P.S. KAKRAHAWA ROOM NO-1</t>
@@ -1457,8 +1538,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1474,7 +1563,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1482,12 +1571,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1786,94 +1893,175 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:28">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:28">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>454</v>
+        <v>481</v>
       </c>
       <c r="D2" t="s">
-        <v>455</v>
+        <v>482</v>
       </c>
       <c r="E2" t="s">
-        <v>456</v>
+        <v>483</v>
       </c>
       <c r="F2" t="s">
-        <v>457</v>
+        <v>484</v>
       </c>
       <c r="G2" t="s">
-        <v>458</v>
+        <v>485</v>
       </c>
       <c r="H2" t="s">
-        <v>459</v>
+        <v>486</v>
       </c>
       <c r="I2" t="s">
-        <v>460</v>
+        <v>487</v>
       </c>
       <c r="J2" t="s">
-        <v>461</v>
+        <v>488</v>
       </c>
       <c r="K2" t="s">
-        <v>462</v>
+        <v>489</v>
       </c>
       <c r="L2" t="s">
-        <v>463</v>
+        <v>490</v>
       </c>
       <c r="M2" t="s">
-        <v>464</v>
+        <v>491</v>
       </c>
       <c r="N2" t="s">
-        <v>465</v>
+        <v>492</v>
       </c>
       <c r="O2" t="s">
-        <v>466</v>
+        <v>493</v>
       </c>
       <c r="P2" t="s">
-        <v>467</v>
+        <v>494</v>
       </c>
       <c r="Q2" t="s">
-        <v>468</v>
+        <v>495</v>
       </c>
       <c r="R2" t="s">
-        <v>469</v>
+        <v>496</v>
       </c>
       <c r="S2" t="s">
-        <v>470</v>
+        <v>497</v>
       </c>
       <c r="T2" t="s">
-        <v>471</v>
+        <v>498</v>
       </c>
       <c r="U2" t="s">
-        <v>472</v>
+        <v>499</v>
       </c>
       <c r="V2" t="s">
-        <v>473</v>
+        <v>500</v>
       </c>
       <c r="W2" t="s">
-        <v>474</v>
+        <v>501</v>
       </c>
       <c r="X2" t="s">
-        <v>475</v>
+        <v>502</v>
       </c>
       <c r="Y2" t="s">
-        <v>476</v>
+        <v>503</v>
       </c>
       <c r="Z2" t="s">
-        <v>476</v>
+        <v>503</v>
       </c>
       <c r="AA2" t="s">
-        <v>477</v>
+        <v>504</v>
       </c>
       <c r="AB2" t="s">
-        <v>478</v>
+        <v>505</v>
       </c>
     </row>
     <row r="3" spans="1:28">
@@ -1881,7 +2069,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="C3">
         <v>651</v>
@@ -1967,7 +2155,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="C4">
         <v>725</v>
@@ -2053,7 +2241,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="C5">
         <v>1104</v>
@@ -2139,7 +2327,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="C6">
         <v>1088</v>
@@ -2225,7 +2413,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="C7">
         <v>1017</v>
@@ -2311,7 +2499,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="C8">
         <v>1064</v>
@@ -2397,7 +2585,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="C9">
         <v>1035</v>
@@ -2483,7 +2671,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="C10">
         <v>1024</v>
@@ -2569,7 +2757,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="C11">
         <v>891</v>
@@ -2655,7 +2843,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="C12">
         <v>803</v>
@@ -2741,7 +2929,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="C13">
         <v>566</v>
@@ -2827,7 +3015,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="C14">
         <v>598</v>
@@ -2913,7 +3101,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="C15">
         <v>716</v>
@@ -2999,7 +3187,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="C16">
         <v>710</v>
@@ -3085,7 +3273,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="C17">
         <v>479</v>
@@ -3171,7 +3359,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="C18">
         <v>636</v>
@@ -3257,7 +3445,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="C19">
         <v>545</v>
@@ -3343,7 +3531,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="C20">
         <v>855</v>
@@ -3429,7 +3617,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="C21">
         <v>806</v>
@@ -3515,7 +3703,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="C22">
         <v>1171</v>
@@ -3601,7 +3789,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="C23">
         <v>898</v>
@@ -3687,7 +3875,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="C24">
         <v>791</v>
@@ -3773,7 +3961,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="C25">
         <v>706</v>
@@ -3859,7 +4047,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="C26">
         <v>760</v>
@@ -3945,7 +4133,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="C27">
         <v>978</v>
@@ -4031,7 +4219,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="C28">
         <v>798</v>
@@ -4117,7 +4305,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="C29">
         <v>681</v>
@@ -4203,7 +4391,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="C30">
         <v>1103</v>
@@ -4289,7 +4477,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="C31">
         <v>972</v>
@@ -4375,7 +4563,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="C32">
         <v>1069</v>
@@ -4461,7 +4649,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="C33">
         <v>818</v>
@@ -4547,7 +4735,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="C34">
         <v>793</v>
@@ -4633,7 +4821,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="C35">
         <v>1049</v>
@@ -4719,7 +4907,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="C36">
         <v>825</v>
@@ -4805,7 +4993,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="C37">
         <v>875</v>
@@ -4891,7 +5079,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="C38">
         <v>1096</v>
@@ -4977,7 +5165,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="C39">
         <v>1032</v>
@@ -5063,7 +5251,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="C40">
         <v>933</v>
@@ -5149,7 +5337,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="C41">
         <v>1073</v>
@@ -5235,7 +5423,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="C42">
         <v>825</v>
@@ -5321,7 +5509,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="C43">
         <v>877</v>
@@ -5407,7 +5595,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="C44">
         <v>855</v>
@@ -5493,7 +5681,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="C45">
         <v>773</v>
@@ -5579,7 +5767,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="C46">
         <v>640</v>
@@ -5665,7 +5853,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="C47">
         <v>1044</v>
@@ -5751,7 +5939,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="C48">
         <v>1074</v>
@@ -5837,7 +6025,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="C49">
         <v>1056</v>
@@ -5923,7 +6111,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="C50">
         <v>687</v>
@@ -6009,7 +6197,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>51</v>
+        <v>78</v>
       </c>
       <c r="C51">
         <v>649</v>
@@ -6095,7 +6283,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="C52">
         <v>653</v>
@@ -6181,7 +6369,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="C53">
         <v>605</v>
@@ -6267,7 +6455,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>54</v>
+        <v>81</v>
       </c>
       <c r="C54">
         <v>826</v>
@@ -6353,7 +6541,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="C55">
         <v>1031</v>
@@ -6439,7 +6627,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="C56">
         <v>896</v>
@@ -6525,7 +6713,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>57</v>
+        <v>84</v>
       </c>
       <c r="C57">
         <v>774</v>
@@ -6611,7 +6799,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="C58">
         <v>705</v>
@@ -6697,7 +6885,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="C59">
         <v>857</v>
@@ -6783,7 +6971,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="C60">
         <v>767</v>
@@ -6869,7 +7057,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="C61">
         <v>871</v>
@@ -6955,7 +7143,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="C62">
         <v>740</v>
@@ -7041,7 +7229,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>63</v>
+        <v>90</v>
       </c>
       <c r="C63">
         <v>655</v>
@@ -7127,7 +7315,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>64</v>
+        <v>91</v>
       </c>
       <c r="C64">
         <v>835</v>
@@ -7213,7 +7401,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="C65">
         <v>743</v>
@@ -7299,7 +7487,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="C66">
         <v>1151</v>
@@ -7385,7 +7573,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>67</v>
+        <v>94</v>
       </c>
       <c r="C67">
         <v>1114</v>
@@ -7471,7 +7659,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="C68">
         <v>1018</v>
@@ -7557,7 +7745,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="C69">
         <v>675</v>
@@ -7643,7 +7831,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="C70">
         <v>863</v>
@@ -7729,7 +7917,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>71</v>
+        <v>98</v>
       </c>
       <c r="C71">
         <v>723</v>
@@ -7815,7 +8003,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="C72">
         <v>1055</v>
@@ -7901,7 +8089,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>73</v>
+        <v>100</v>
       </c>
       <c r="C73">
         <v>984</v>
@@ -7987,7 +8175,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>74</v>
+        <v>101</v>
       </c>
       <c r="C74">
         <v>937</v>
@@ -8073,7 +8261,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>75</v>
+        <v>102</v>
       </c>
       <c r="C75">
         <v>627</v>
@@ -8159,7 +8347,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>76</v>
+        <v>103</v>
       </c>
       <c r="C76">
         <v>664</v>
@@ -8245,7 +8433,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="C77">
         <v>1081</v>
@@ -8331,7 +8519,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="C78">
         <v>1077</v>
@@ -8417,7 +8605,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>79</v>
+        <v>106</v>
       </c>
       <c r="C79">
         <v>1033</v>
@@ -8503,7 +8691,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>80</v>
+        <v>107</v>
       </c>
       <c r="C80">
         <v>1001</v>
@@ -8589,7 +8777,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="C81">
         <v>1053</v>
@@ -8675,7 +8863,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="C82">
         <v>1040</v>
@@ -8761,7 +8949,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="C83">
         <v>880</v>
@@ -8847,7 +9035,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="C84">
         <v>722</v>
@@ -8933,7 +9121,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="C85">
         <v>1076</v>
@@ -9019,7 +9207,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C86">
         <v>394</v>
@@ -9105,7 +9293,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>87</v>
+        <v>114</v>
       </c>
       <c r="C87">
         <v>804</v>
@@ -9191,7 +9379,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>88</v>
+        <v>115</v>
       </c>
       <c r="C88">
         <v>1029</v>
@@ -9277,7 +9465,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
       <c r="C89">
         <v>1027</v>
@@ -9363,7 +9551,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>90</v>
+        <v>117</v>
       </c>
       <c r="C90">
         <v>636</v>
@@ -9449,7 +9637,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>91</v>
+        <v>118</v>
       </c>
       <c r="C91">
         <v>548</v>
@@ -9535,7 +9723,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>92</v>
+        <v>119</v>
       </c>
       <c r="C92">
         <v>1125</v>
@@ -9621,7 +9809,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>93</v>
+        <v>120</v>
       </c>
       <c r="C93">
         <v>1099</v>
@@ -9707,7 +9895,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>94</v>
+        <v>121</v>
       </c>
       <c r="C94">
         <v>1004</v>
@@ -9793,7 +9981,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>95</v>
+        <v>122</v>
       </c>
       <c r="C95">
         <v>1122</v>
@@ -9879,7 +10067,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="C96">
         <v>987</v>
@@ -9965,7 +10153,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>97</v>
+        <v>124</v>
       </c>
       <c r="C97">
         <v>733</v>
@@ -10051,7 +10239,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="C98">
         <v>908</v>
@@ -10137,7 +10325,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>99</v>
+        <v>126</v>
       </c>
       <c r="C99">
         <v>927</v>
@@ -10223,7 +10411,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="C100">
         <v>841</v>
@@ -10309,7 +10497,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>101</v>
+        <v>128</v>
       </c>
       <c r="C101">
         <v>645</v>
@@ -10395,7 +10583,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>102</v>
+        <v>129</v>
       </c>
       <c r="C102">
         <v>1073</v>
@@ -10481,7 +10669,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="C103">
         <v>907</v>
@@ -10567,7 +10755,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>104</v>
+        <v>131</v>
       </c>
       <c r="C104">
         <v>923</v>
@@ -10653,7 +10841,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="C105">
         <v>978</v>
@@ -10739,7 +10927,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>106</v>
+        <v>133</v>
       </c>
       <c r="C106">
         <v>937</v>
@@ -10825,7 +11013,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>107</v>
+        <v>134</v>
       </c>
       <c r="C107">
         <v>815</v>
@@ -10911,7 +11099,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>108</v>
+        <v>135</v>
       </c>
       <c r="C108">
         <v>875</v>
@@ -10997,7 +11185,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>109</v>
+        <v>136</v>
       </c>
       <c r="C109">
         <v>1051</v>
@@ -11083,7 +11271,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>110</v>
+        <v>137</v>
       </c>
       <c r="C110">
         <v>976</v>
@@ -11169,7 +11357,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>111</v>
+        <v>138</v>
       </c>
       <c r="C111">
         <v>867</v>
@@ -11255,7 +11443,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>112</v>
+        <v>139</v>
       </c>
       <c r="C112">
         <v>806</v>
@@ -11341,7 +11529,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>113</v>
+        <v>140</v>
       </c>
       <c r="C113">
         <v>801</v>
@@ -11427,7 +11615,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="C114">
         <v>1054</v>
@@ -11513,7 +11701,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>115</v>
+        <v>142</v>
       </c>
       <c r="C115">
         <v>992</v>
@@ -11599,7 +11787,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>116</v>
+        <v>143</v>
       </c>
       <c r="C116">
         <v>902</v>
@@ -11685,7 +11873,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>117</v>
+        <v>144</v>
       </c>
       <c r="C117">
         <v>996</v>
@@ -11771,7 +11959,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="C118">
         <v>844</v>
@@ -11857,7 +12045,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="C119">
         <v>737</v>
@@ -11943,7 +12131,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="C120">
         <v>582</v>
@@ -12029,7 +12217,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="C121">
         <v>735</v>
@@ -12115,7 +12303,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>122</v>
+        <v>149</v>
       </c>
       <c r="C122">
         <v>734</v>
@@ -12201,7 +12389,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="C123">
         <v>1016</v>
@@ -12287,7 +12475,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
       <c r="C124">
         <v>883</v>
@@ -12373,7 +12561,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>125</v>
+        <v>152</v>
       </c>
       <c r="C125">
         <v>679</v>
@@ -12459,7 +12647,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>126</v>
+        <v>153</v>
       </c>
       <c r="C126">
         <v>787</v>
@@ -12545,7 +12733,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>127</v>
+        <v>154</v>
       </c>
       <c r="C127">
         <v>824</v>
@@ -12631,7 +12819,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="C128">
         <v>694</v>
@@ -12717,7 +12905,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>129</v>
+        <v>156</v>
       </c>
       <c r="C129">
         <v>898</v>
@@ -12803,7 +12991,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>130</v>
+        <v>157</v>
       </c>
       <c r="C130">
         <v>861</v>
@@ -12889,7 +13077,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>131</v>
+        <v>158</v>
       </c>
       <c r="C131">
         <v>873</v>
@@ -12975,7 +13163,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>132</v>
+        <v>159</v>
       </c>
       <c r="C132">
         <v>668</v>
@@ -13061,7 +13249,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>133</v>
+        <v>160</v>
       </c>
       <c r="C133">
         <v>926</v>
@@ -13147,7 +13335,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>134</v>
+        <v>161</v>
       </c>
       <c r="C134">
         <v>847</v>
@@ -13233,7 +13421,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>135</v>
+        <v>162</v>
       </c>
       <c r="C135">
         <v>724</v>
@@ -13319,7 +13507,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>136</v>
+        <v>163</v>
       </c>
       <c r="C136">
         <v>1122</v>
@@ -13405,7 +13593,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>137</v>
+        <v>164</v>
       </c>
       <c r="C137">
         <v>1134</v>
@@ -13491,7 +13679,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>138</v>
+        <v>165</v>
       </c>
       <c r="C138">
         <v>967</v>
@@ -13577,7 +13765,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>139</v>
+        <v>166</v>
       </c>
       <c r="C139">
         <v>887</v>
@@ -13663,7 +13851,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>140</v>
+        <v>167</v>
       </c>
       <c r="C140">
         <v>841</v>
@@ -13749,7 +13937,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>141</v>
+        <v>168</v>
       </c>
       <c r="C141">
         <v>958</v>
@@ -13835,7 +14023,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>142</v>
+        <v>169</v>
       </c>
       <c r="C142">
         <v>691</v>
@@ -13921,7 +14109,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>143</v>
+        <v>170</v>
       </c>
       <c r="C143">
         <v>709</v>
@@ -14007,7 +14195,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>144</v>
+        <v>171</v>
       </c>
       <c r="C144">
         <v>1089</v>
@@ -14093,7 +14281,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>145</v>
+        <v>172</v>
       </c>
       <c r="C145">
         <v>643</v>
@@ -14179,7 +14367,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>146</v>
+        <v>173</v>
       </c>
       <c r="C146">
         <v>540</v>
@@ -14265,7 +14453,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>147</v>
+        <v>174</v>
       </c>
       <c r="C147">
         <v>819</v>
@@ -14351,7 +14539,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>148</v>
+        <v>175</v>
       </c>
       <c r="C148">
         <v>837</v>
@@ -14437,7 +14625,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>149</v>
+        <v>176</v>
       </c>
       <c r="C149">
         <v>876</v>
@@ -14523,7 +14711,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>150</v>
+        <v>177</v>
       </c>
       <c r="C150">
         <v>965</v>
@@ -14609,7 +14797,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>151</v>
+        <v>178</v>
       </c>
       <c r="C151">
         <v>941</v>
@@ -14695,7 +14883,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>152</v>
+        <v>179</v>
       </c>
       <c r="C152">
         <v>1115</v>
@@ -14781,7 +14969,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>153</v>
+        <v>180</v>
       </c>
       <c r="C153">
         <v>712</v>
@@ -14867,7 +15055,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>154</v>
+        <v>181</v>
       </c>
       <c r="C154">
         <v>657</v>
@@ -14953,7 +15141,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>155</v>
+        <v>182</v>
       </c>
       <c r="C155">
         <v>1044</v>
@@ -15039,7 +15227,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="C156">
         <v>557</v>
@@ -15125,7 +15313,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>157</v>
+        <v>184</v>
       </c>
       <c r="C157">
         <v>987</v>
@@ -15211,7 +15399,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>158</v>
+        <v>185</v>
       </c>
       <c r="C158">
         <v>859</v>
@@ -15297,7 +15485,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>159</v>
+        <v>186</v>
       </c>
       <c r="C159">
         <v>690</v>
@@ -15383,7 +15571,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>160</v>
+        <v>187</v>
       </c>
       <c r="C160">
         <v>787</v>
@@ -15469,7 +15657,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>161</v>
+        <v>188</v>
       </c>
       <c r="C161">
         <v>935</v>
@@ -15555,7 +15743,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>162</v>
+        <v>189</v>
       </c>
       <c r="C162">
         <v>651</v>
@@ -15641,7 +15829,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>163</v>
+        <v>190</v>
       </c>
       <c r="C163">
         <v>720</v>
@@ -15727,7 +15915,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>164</v>
+        <v>191</v>
       </c>
       <c r="C164">
         <v>593</v>
@@ -15813,7 +16001,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>165</v>
+        <v>192</v>
       </c>
       <c r="C165">
         <v>838</v>
@@ -15899,7 +16087,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>166</v>
+        <v>193</v>
       </c>
       <c r="C166">
         <v>532</v>
@@ -15985,7 +16173,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>167</v>
+        <v>194</v>
       </c>
       <c r="C167">
         <v>866</v>
@@ -16071,7 +16259,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>168</v>
+        <v>195</v>
       </c>
       <c r="C168">
         <v>1022</v>
@@ -16157,7 +16345,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>169</v>
+        <v>196</v>
       </c>
       <c r="C169">
         <v>893</v>
@@ -16243,7 +16431,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>170</v>
+        <v>197</v>
       </c>
       <c r="C170">
         <v>1006</v>
@@ -16329,7 +16517,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>171</v>
+        <v>198</v>
       </c>
       <c r="C171">
         <v>944</v>
@@ -16415,7 +16603,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>172</v>
+        <v>199</v>
       </c>
       <c r="C172">
         <v>871</v>
@@ -16501,7 +16689,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="C173">
         <v>957</v>
@@ -16587,7 +16775,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>174</v>
+        <v>201</v>
       </c>
       <c r="C174">
         <v>817</v>
@@ -16673,7 +16861,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>175</v>
+        <v>202</v>
       </c>
       <c r="C175">
         <v>1102</v>
@@ -16759,7 +16947,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>176</v>
+        <v>203</v>
       </c>
       <c r="C176">
         <v>945</v>
@@ -16845,7 +17033,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>177</v>
+        <v>204</v>
       </c>
       <c r="C177">
         <v>486</v>
@@ -16931,7 +17119,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>178</v>
+        <v>205</v>
       </c>
       <c r="C178">
         <v>595</v>
@@ -17017,7 +17205,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>179</v>
+        <v>206</v>
       </c>
       <c r="C179">
         <v>876</v>
@@ -17103,7 +17291,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>180</v>
+        <v>207</v>
       </c>
       <c r="C180">
         <v>1024</v>
@@ -17189,7 +17377,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>181</v>
+        <v>208</v>
       </c>
       <c r="C181">
         <v>724</v>
@@ -17275,7 +17463,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>182</v>
+        <v>209</v>
       </c>
       <c r="C182">
         <v>785</v>
@@ -17361,7 +17549,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>183</v>
+        <v>210</v>
       </c>
       <c r="C183">
         <v>724</v>
@@ -17447,7 +17635,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>184</v>
+        <v>211</v>
       </c>
       <c r="C184">
         <v>802</v>
@@ -17533,7 +17721,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>185</v>
+        <v>212</v>
       </c>
       <c r="C185">
         <v>1103</v>
@@ -17619,7 +17807,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>186</v>
+        <v>213</v>
       </c>
       <c r="C186">
         <v>892</v>
@@ -17705,7 +17893,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>187</v>
+        <v>214</v>
       </c>
       <c r="C187">
         <v>807</v>
@@ -17791,7 +17979,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>188</v>
+        <v>215</v>
       </c>
       <c r="C188">
         <v>722</v>
@@ -17877,7 +18065,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>189</v>
+        <v>216</v>
       </c>
       <c r="C189">
         <v>655</v>
@@ -17963,7 +18151,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>190</v>
+        <v>217</v>
       </c>
       <c r="C190">
         <v>748</v>
@@ -18049,7 +18237,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>191</v>
+        <v>218</v>
       </c>
       <c r="C191">
         <v>915</v>
@@ -18135,7 +18323,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>192</v>
+        <v>219</v>
       </c>
       <c r="C192">
         <v>632</v>
@@ -18221,7 +18409,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>193</v>
+        <v>220</v>
       </c>
       <c r="C193">
         <v>711</v>
@@ -18307,7 +18495,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>194</v>
+        <v>221</v>
       </c>
       <c r="C194">
         <v>847</v>
@@ -18393,7 +18581,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>195</v>
+        <v>222</v>
       </c>
       <c r="C195">
         <v>658</v>
@@ -18479,7 +18667,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>196</v>
+        <v>223</v>
       </c>
       <c r="C196">
         <v>952</v>
@@ -18565,7 +18753,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>197</v>
+        <v>224</v>
       </c>
       <c r="C197">
         <v>883</v>
@@ -18651,7 +18839,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>198</v>
+        <v>225</v>
       </c>
       <c r="C198">
         <v>849</v>
@@ -18737,7 +18925,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>199</v>
+        <v>226</v>
       </c>
       <c r="C199">
         <v>1180</v>
@@ -18823,7 +19011,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>200</v>
+        <v>227</v>
       </c>
       <c r="C200">
         <v>996</v>
@@ -18909,7 +19097,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>201</v>
+        <v>228</v>
       </c>
       <c r="C201">
         <v>671</v>
@@ -18995,7 +19183,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>202</v>
+        <v>229</v>
       </c>
       <c r="C202">
         <v>753</v>
@@ -19081,7 +19269,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>203</v>
+        <v>230</v>
       </c>
       <c r="C203">
         <v>963</v>
@@ -19167,7 +19355,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>204</v>
+        <v>231</v>
       </c>
       <c r="C204">
         <v>978</v>
@@ -19253,7 +19441,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>205</v>
+        <v>232</v>
       </c>
       <c r="C205">
         <v>826</v>
@@ -19339,7 +19527,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>206</v>
+        <v>233</v>
       </c>
       <c r="C206">
         <v>939</v>
@@ -19425,7 +19613,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>207</v>
+        <v>234</v>
       </c>
       <c r="C207">
         <v>907</v>
@@ -19511,7 +19699,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>208</v>
+        <v>235</v>
       </c>
       <c r="C208">
         <v>1124</v>
@@ -19597,7 +19785,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>209</v>
+        <v>236</v>
       </c>
       <c r="C209">
         <v>1107</v>
@@ -19683,7 +19871,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>210</v>
+        <v>237</v>
       </c>
       <c r="C210">
         <v>1105</v>
@@ -19769,7 +19957,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="C211">
         <v>1007</v>
@@ -19855,7 +20043,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>212</v>
+        <v>239</v>
       </c>
       <c r="C212">
         <v>824</v>
@@ -19941,7 +20129,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>213</v>
+        <v>240</v>
       </c>
       <c r="C213">
         <v>1045</v>
@@ -20027,7 +20215,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>214</v>
+        <v>241</v>
       </c>
       <c r="C214">
         <v>1021</v>
@@ -20113,7 +20301,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>215</v>
+        <v>242</v>
       </c>
       <c r="C215">
         <v>617</v>
@@ -20199,7 +20387,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>216</v>
+        <v>243</v>
       </c>
       <c r="C216">
         <v>673</v>
@@ -20285,7 +20473,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>217</v>
+        <v>244</v>
       </c>
       <c r="C217">
         <v>1098</v>
@@ -20371,7 +20559,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>218</v>
+        <v>245</v>
       </c>
       <c r="C218">
         <v>1184</v>
@@ -20457,7 +20645,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>219</v>
+        <v>246</v>
       </c>
       <c r="C219">
         <v>1104</v>
@@ -20543,7 +20731,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>220</v>
+        <v>247</v>
       </c>
       <c r="C220">
         <v>938</v>
@@ -20629,7 +20817,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>221</v>
+        <v>248</v>
       </c>
       <c r="C221">
         <v>1073</v>
@@ -20715,7 +20903,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>222</v>
+        <v>249</v>
       </c>
       <c r="C222">
         <v>967</v>
@@ -20801,7 +20989,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>223</v>
+        <v>250</v>
       </c>
       <c r="C223">
         <v>937</v>
@@ -20887,7 +21075,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>224</v>
+        <v>251</v>
       </c>
       <c r="C224">
         <v>707</v>
@@ -20973,7 +21161,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>225</v>
+        <v>252</v>
       </c>
       <c r="C225">
         <v>865</v>
@@ -21059,7 +21247,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>226</v>
+        <v>253</v>
       </c>
       <c r="C226">
         <v>598</v>
@@ -21145,7 +21333,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>227</v>
+        <v>254</v>
       </c>
       <c r="C227">
         <v>967</v>
@@ -21231,7 +21419,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>228</v>
+        <v>255</v>
       </c>
       <c r="C228">
         <v>1035</v>
@@ -21317,7 +21505,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>229</v>
+        <v>256</v>
       </c>
       <c r="C229">
         <v>1092</v>
@@ -21403,7 +21591,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>230</v>
+        <v>257</v>
       </c>
       <c r="C230">
         <v>892</v>
@@ -21489,7 +21677,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>231</v>
+        <v>258</v>
       </c>
       <c r="C231">
         <v>1048</v>
@@ -21575,7 +21763,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>232</v>
+        <v>259</v>
       </c>
       <c r="C232">
         <v>1089</v>
@@ -21661,7 +21849,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>233</v>
+        <v>260</v>
       </c>
       <c r="C233">
         <v>833</v>
@@ -21747,7 +21935,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>234</v>
+        <v>261</v>
       </c>
       <c r="C234">
         <v>914</v>
@@ -21833,7 +22021,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>235</v>
+        <v>262</v>
       </c>
       <c r="C235">
         <v>1023</v>
@@ -21919,7 +22107,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>236</v>
+        <v>263</v>
       </c>
       <c r="C236">
         <v>725</v>
@@ -22005,7 +22193,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>237</v>
+        <v>264</v>
       </c>
       <c r="C237">
         <v>1016</v>
@@ -22091,7 +22279,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>238</v>
+        <v>265</v>
       </c>
       <c r="C238">
         <v>642</v>
@@ -22177,7 +22365,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>239</v>
+        <v>266</v>
       </c>
       <c r="C239">
         <v>585</v>
@@ -22263,7 +22451,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>240</v>
+        <v>267</v>
       </c>
       <c r="C240">
         <v>1125</v>
@@ -22349,7 +22537,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>241</v>
+        <v>268</v>
       </c>
       <c r="C241">
         <v>617</v>
@@ -22435,7 +22623,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>242</v>
+        <v>269</v>
       </c>
       <c r="C242">
         <v>685</v>
@@ -22521,7 +22709,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>243</v>
+        <v>270</v>
       </c>
       <c r="C243">
         <v>974</v>
@@ -22607,7 +22795,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>244</v>
+        <v>271</v>
       </c>
       <c r="C244">
         <v>639</v>
@@ -22693,7 +22881,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>245</v>
+        <v>272</v>
       </c>
       <c r="C245">
         <v>704</v>
@@ -22779,7 +22967,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>246</v>
+        <v>273</v>
       </c>
       <c r="C246">
         <v>1071</v>
@@ -22865,7 +23053,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>247</v>
+        <v>274</v>
       </c>
       <c r="C247">
         <v>1035</v>
@@ -22951,7 +23139,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>248</v>
+        <v>275</v>
       </c>
       <c r="C248">
         <v>937</v>
@@ -23037,7 +23225,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>249</v>
+        <v>276</v>
       </c>
       <c r="C249">
         <v>858</v>
@@ -23123,7 +23311,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>250</v>
+        <v>277</v>
       </c>
       <c r="C250">
         <v>830</v>
@@ -23209,7 +23397,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>251</v>
+        <v>278</v>
       </c>
       <c r="C251">
         <v>1160</v>
@@ -23295,7 +23483,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>252</v>
+        <v>279</v>
       </c>
       <c r="C252">
         <v>710</v>
@@ -23381,7 +23569,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>253</v>
+        <v>280</v>
       </c>
       <c r="C253">
         <v>1043</v>
@@ -23467,7 +23655,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>254</v>
+        <v>281</v>
       </c>
       <c r="C254">
         <v>715</v>
@@ -23553,7 +23741,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>255</v>
+        <v>282</v>
       </c>
       <c r="C255">
         <v>1096</v>
@@ -23639,7 +23827,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>256</v>
+        <v>283</v>
       </c>
       <c r="C256">
         <v>1012</v>
@@ -23725,7 +23913,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>257</v>
+        <v>284</v>
       </c>
       <c r="C257">
         <v>958</v>
@@ -23811,7 +23999,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="C258">
         <v>1135</v>
@@ -23897,7 +24085,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>259</v>
+        <v>286</v>
       </c>
       <c r="C259">
         <v>1100</v>
@@ -23983,7 +24171,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>260</v>
+        <v>287</v>
       </c>
       <c r="C260">
         <v>1134</v>
@@ -24069,7 +24257,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>261</v>
+        <v>288</v>
       </c>
       <c r="C261">
         <v>997</v>
@@ -24155,7 +24343,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>262</v>
+        <v>289</v>
       </c>
       <c r="C262">
         <v>1100</v>
@@ -24241,7 +24429,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>263</v>
+        <v>290</v>
       </c>
       <c r="C263">
         <v>1146</v>
@@ -24327,7 +24515,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>264</v>
+        <v>291</v>
       </c>
       <c r="C264">
         <v>1121</v>
@@ -24413,7 +24601,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>265</v>
+        <v>292</v>
       </c>
       <c r="C265">
         <v>836</v>
@@ -24499,7 +24687,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="C266">
         <v>1126</v>
@@ -24585,7 +24773,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>267</v>
+        <v>294</v>
       </c>
       <c r="C267">
         <v>534</v>
@@ -24671,7 +24859,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>268</v>
+        <v>295</v>
       </c>
       <c r="C268">
         <v>920</v>
@@ -24757,7 +24945,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>269</v>
+        <v>296</v>
       </c>
       <c r="C269">
         <v>938</v>
@@ -24843,7 +25031,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>270</v>
+        <v>297</v>
       </c>
       <c r="C270">
         <v>949</v>
@@ -24929,7 +25117,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>271</v>
+        <v>298</v>
       </c>
       <c r="C271">
         <v>810</v>
@@ -25015,7 +25203,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>272</v>
+        <v>299</v>
       </c>
       <c r="C272">
         <v>913</v>
@@ -25101,7 +25289,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>273</v>
+        <v>300</v>
       </c>
       <c r="C273">
         <v>1065</v>
@@ -25187,7 +25375,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>274</v>
+        <v>301</v>
       </c>
       <c r="C274">
         <v>904</v>
@@ -25273,7 +25461,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>275</v>
+        <v>302</v>
       </c>
       <c r="C275">
         <v>737</v>
@@ -25359,7 +25547,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>276</v>
+        <v>303</v>
       </c>
       <c r="C276">
         <v>1062</v>
@@ -25445,7 +25633,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>277</v>
+        <v>304</v>
       </c>
       <c r="C277">
         <v>656</v>
@@ -25531,7 +25719,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>278</v>
+        <v>305</v>
       </c>
       <c r="C278">
         <v>668</v>
@@ -25617,7 +25805,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>279</v>
+        <v>306</v>
       </c>
       <c r="C279">
         <v>1087</v>
@@ -25703,7 +25891,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>280</v>
+        <v>307</v>
       </c>
       <c r="C280">
         <v>1075</v>
@@ -25789,7 +25977,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>281</v>
+        <v>308</v>
       </c>
       <c r="C281">
         <v>1045</v>
@@ -25875,7 +26063,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>282</v>
+        <v>309</v>
       </c>
       <c r="C282">
         <v>1085</v>
@@ -25961,7 +26149,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>283</v>
+        <v>310</v>
       </c>
       <c r="C283">
         <v>667</v>
@@ -26047,7 +26235,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>284</v>
+        <v>311</v>
       </c>
       <c r="C284">
         <v>861</v>
@@ -26133,7 +26321,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>285</v>
+        <v>312</v>
       </c>
       <c r="C285">
         <v>806</v>
@@ -26219,7 +26407,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>286</v>
+        <v>313</v>
       </c>
       <c r="C286">
         <v>771</v>
@@ -26305,7 +26493,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>287</v>
+        <v>314</v>
       </c>
       <c r="C287">
         <v>695</v>
@@ -26391,7 +26579,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>288</v>
+        <v>315</v>
       </c>
       <c r="C288">
         <v>822</v>
@@ -26477,7 +26665,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>289</v>
+        <v>316</v>
       </c>
       <c r="C289">
         <v>730</v>
@@ -26563,7 +26751,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>290</v>
+        <v>317</v>
       </c>
       <c r="C290">
         <v>955</v>
@@ -26649,7 +26837,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>291</v>
+        <v>318</v>
       </c>
       <c r="C291">
         <v>1145</v>
@@ -26735,7 +26923,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>292</v>
+        <v>319</v>
       </c>
       <c r="C292">
         <v>811</v>
@@ -26821,7 +27009,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>293</v>
+        <v>320</v>
       </c>
       <c r="C293">
         <v>738</v>
@@ -26907,7 +27095,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>294</v>
+        <v>321</v>
       </c>
       <c r="C294">
         <v>1034</v>
@@ -26993,7 +27181,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>295</v>
+        <v>322</v>
       </c>
       <c r="C295">
         <v>993</v>
@@ -27079,7 +27267,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>296</v>
+        <v>323</v>
       </c>
       <c r="C296">
         <v>759</v>
@@ -27165,7 +27353,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>297</v>
+        <v>324</v>
       </c>
       <c r="C297">
         <v>989</v>
@@ -27251,7 +27439,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>298</v>
+        <v>325</v>
       </c>
       <c r="C298">
         <v>539</v>
@@ -27337,7 +27525,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>299</v>
+        <v>326</v>
       </c>
       <c r="C299">
         <v>835</v>
@@ -27423,7 +27611,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>300</v>
+        <v>327</v>
       </c>
       <c r="C300">
         <v>814</v>
@@ -27509,7 +27697,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>301</v>
+        <v>328</v>
       </c>
       <c r="C301">
         <v>877</v>
@@ -27595,7 +27783,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>302</v>
+        <v>329</v>
       </c>
       <c r="C302">
         <v>760</v>
@@ -27681,7 +27869,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>303</v>
+        <v>330</v>
       </c>
       <c r="C303">
         <v>1043</v>
@@ -27767,7 +27955,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>304</v>
+        <v>331</v>
       </c>
       <c r="C304">
         <v>1012</v>
@@ -27853,7 +28041,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>305</v>
+        <v>332</v>
       </c>
       <c r="C305">
         <v>847</v>
@@ -27939,7 +28127,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>306</v>
+        <v>333</v>
       </c>
       <c r="C306">
         <v>1166</v>
@@ -28025,7 +28213,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>307</v>
+        <v>334</v>
       </c>
       <c r="C307">
         <v>1072</v>
@@ -28111,7 +28299,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>308</v>
+        <v>335</v>
       </c>
       <c r="C308">
         <v>1150</v>
@@ -28197,7 +28385,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>309</v>
+        <v>336</v>
       </c>
       <c r="C309">
         <v>1162</v>
@@ -28283,7 +28471,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>310</v>
+        <v>337</v>
       </c>
       <c r="C310">
         <v>1051</v>
@@ -28369,7 +28557,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>311</v>
+        <v>338</v>
       </c>
       <c r="C311">
         <v>1096</v>
@@ -28455,7 +28643,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>312</v>
+        <v>339</v>
       </c>
       <c r="C312">
         <v>1119</v>
@@ -28541,7 +28729,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>313</v>
+        <v>340</v>
       </c>
       <c r="C313">
         <v>1176</v>
@@ -28627,7 +28815,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>314</v>
+        <v>341</v>
       </c>
       <c r="C314">
         <v>1156</v>
@@ -28713,7 +28901,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>315</v>
+        <v>342</v>
       </c>
       <c r="C315">
         <v>1163</v>
@@ -28799,7 +28987,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>316</v>
+        <v>343</v>
       </c>
       <c r="C316">
         <v>870</v>
@@ -28885,7 +29073,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>317</v>
+        <v>344</v>
       </c>
       <c r="C317">
         <v>1008</v>
@@ -28971,7 +29159,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>318</v>
+        <v>345</v>
       </c>
       <c r="C318">
         <v>1148</v>
@@ -29057,7 +29245,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>319</v>
+        <v>346</v>
       </c>
       <c r="C319">
         <v>1081</v>
@@ -29143,7 +29331,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>320</v>
+        <v>347</v>
       </c>
       <c r="C320">
         <v>642</v>
@@ -29229,7 +29417,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>321</v>
+        <v>348</v>
       </c>
       <c r="C321">
         <v>1045</v>
@@ -29315,7 +29503,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>322</v>
+        <v>349</v>
       </c>
       <c r="C322">
         <v>1042</v>
@@ -29401,7 +29589,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>323</v>
+        <v>350</v>
       </c>
       <c r="C323">
         <v>1046</v>
@@ -29487,7 +29675,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>324</v>
+        <v>351</v>
       </c>
       <c r="C324">
         <v>1124</v>
@@ -29573,7 +29761,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>325</v>
+        <v>352</v>
       </c>
       <c r="C325">
         <v>1157</v>
@@ -29659,7 +29847,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>326</v>
+        <v>353</v>
       </c>
       <c r="C326">
         <v>1043</v>
@@ -29745,7 +29933,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>327</v>
+        <v>354</v>
       </c>
       <c r="C327">
         <v>884</v>
@@ -29831,7 +30019,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>328</v>
+        <v>355</v>
       </c>
       <c r="C328">
         <v>1077</v>
@@ -29917,7 +30105,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>329</v>
+        <v>356</v>
       </c>
       <c r="C329">
         <v>966</v>
@@ -30003,7 +30191,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>330</v>
+        <v>357</v>
       </c>
       <c r="C330">
         <v>844</v>
@@ -30089,7 +30277,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>331</v>
+        <v>358</v>
       </c>
       <c r="C331">
         <v>739</v>
@@ -30175,7 +30363,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>332</v>
+        <v>359</v>
       </c>
       <c r="C332">
         <v>892</v>
@@ -30261,7 +30449,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>333</v>
+        <v>360</v>
       </c>
       <c r="C333">
         <v>664</v>
@@ -30347,7 +30535,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>334</v>
+        <v>361</v>
       </c>
       <c r="C334">
         <v>594</v>
@@ -30433,7 +30621,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>335</v>
+        <v>362</v>
       </c>
       <c r="C335">
         <v>1036</v>
@@ -30519,7 +30707,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>336</v>
+        <v>363</v>
       </c>
       <c r="C336">
         <v>979</v>
@@ -30605,7 +30793,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>337</v>
+        <v>364</v>
       </c>
       <c r="C337">
         <v>1127</v>
@@ -30691,7 +30879,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>338</v>
+        <v>365</v>
       </c>
       <c r="C338">
         <v>855</v>
@@ -30777,7 +30965,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>339</v>
+        <v>366</v>
       </c>
       <c r="C339">
         <v>1074</v>
@@ -30863,7 +31051,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>340</v>
+        <v>367</v>
       </c>
       <c r="C340">
         <v>1094</v>
@@ -30949,7 +31137,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>341</v>
+        <v>368</v>
       </c>
       <c r="C341">
         <v>1137</v>
@@ -31035,7 +31223,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>342</v>
+        <v>369</v>
       </c>
       <c r="C342">
         <v>1040</v>
@@ -31121,7 +31309,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>343</v>
+        <v>370</v>
       </c>
       <c r="C343">
         <v>1130</v>
@@ -31207,7 +31395,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>344</v>
+        <v>371</v>
       </c>
       <c r="C344">
         <v>652</v>
@@ -31293,7 +31481,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>345</v>
+        <v>372</v>
       </c>
       <c r="C345">
         <v>596</v>
@@ -31379,7 +31567,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>346</v>
+        <v>373</v>
       </c>
       <c r="C346">
         <v>1084</v>
@@ -31465,7 +31653,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>347</v>
+        <v>374</v>
       </c>
       <c r="C347">
         <v>661</v>
@@ -31551,7 +31739,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>348</v>
+        <v>375</v>
       </c>
       <c r="C348">
         <v>748</v>
@@ -31637,7 +31825,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>349</v>
+        <v>376</v>
       </c>
       <c r="C349">
         <v>708</v>
@@ -31723,7 +31911,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>350</v>
+        <v>377</v>
       </c>
       <c r="C350">
         <v>739</v>
@@ -31809,7 +31997,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>351</v>
+        <v>378</v>
       </c>
       <c r="C351">
         <v>693</v>
@@ -31895,7 +32083,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>352</v>
+        <v>379</v>
       </c>
       <c r="C352">
         <v>470</v>
@@ -31981,7 +32169,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>353</v>
+        <v>380</v>
       </c>
       <c r="C353">
         <v>1009</v>
@@ -32067,7 +32255,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>354</v>
+        <v>381</v>
       </c>
       <c r="C354">
         <v>868</v>
@@ -32153,7 +32341,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>355</v>
+        <v>382</v>
       </c>
       <c r="C355">
         <v>844</v>
@@ -32239,7 +32427,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>356</v>
+        <v>383</v>
       </c>
       <c r="C356">
         <v>815</v>
@@ -32325,7 +32513,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="s">
-        <v>357</v>
+        <v>384</v>
       </c>
       <c r="C357">
         <v>882</v>
@@ -32411,7 +32599,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="s">
-        <v>358</v>
+        <v>385</v>
       </c>
       <c r="C358">
         <v>1133</v>
@@ -32497,7 +32685,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="s">
-        <v>359</v>
+        <v>386</v>
       </c>
       <c r="C359">
         <v>601</v>
@@ -32583,7 +32771,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="s">
-        <v>360</v>
+        <v>387</v>
       </c>
       <c r="C360">
         <v>1054</v>
@@ -32669,7 +32857,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="s">
-        <v>361</v>
+        <v>388</v>
       </c>
       <c r="C361">
         <v>905</v>
@@ -32755,7 +32943,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="s">
-        <v>362</v>
+        <v>389</v>
       </c>
       <c r="C362">
         <v>1000</v>
@@ -32841,7 +33029,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="s">
-        <v>363</v>
+        <v>390</v>
       </c>
       <c r="C363">
         <v>1054</v>
@@ -32927,7 +33115,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="s">
-        <v>364</v>
+        <v>391</v>
       </c>
       <c r="C364">
         <v>1102</v>
@@ -33013,7 +33201,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="s">
-        <v>365</v>
+        <v>392</v>
       </c>
       <c r="C365">
         <v>1032</v>
@@ -33099,7 +33287,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="s">
-        <v>366</v>
+        <v>393</v>
       </c>
       <c r="C366">
         <v>1110</v>
@@ -33185,7 +33373,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="s">
-        <v>367</v>
+        <v>394</v>
       </c>
       <c r="C367">
         <v>1011</v>
@@ -33271,7 +33459,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="s">
-        <v>368</v>
+        <v>395</v>
       </c>
       <c r="C368">
         <v>1180</v>
@@ -33357,7 +33545,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="s">
-        <v>369</v>
+        <v>396</v>
       </c>
       <c r="C369">
         <v>1117</v>
@@ -33443,7 +33631,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="s">
-        <v>370</v>
+        <v>397</v>
       </c>
       <c r="C370">
         <v>1048</v>
@@ -33529,7 +33717,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="s">
-        <v>371</v>
+        <v>398</v>
       </c>
       <c r="C371">
         <v>1008</v>
@@ -33615,7 +33803,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="s">
-        <v>372</v>
+        <v>399</v>
       </c>
       <c r="C372">
         <v>970</v>
@@ -33701,7 +33889,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="s">
-        <v>373</v>
+        <v>400</v>
       </c>
       <c r="C373">
         <v>1181</v>
@@ -33787,7 +33975,7 @@
         <v>372</v>
       </c>
       <c r="B374" t="s">
-        <v>374</v>
+        <v>401</v>
       </c>
       <c r="C374">
         <v>669</v>
@@ -33873,7 +34061,7 @@
         <v>373</v>
       </c>
       <c r="B375" t="s">
-        <v>375</v>
+        <v>402</v>
       </c>
       <c r="C375">
         <v>816</v>
@@ -33959,7 +34147,7 @@
         <v>374</v>
       </c>
       <c r="B376" t="s">
-        <v>376</v>
+        <v>403</v>
       </c>
       <c r="C376">
         <v>991</v>
@@ -34045,7 +34233,7 @@
         <v>375</v>
       </c>
       <c r="B377" t="s">
-        <v>377</v>
+        <v>404</v>
       </c>
       <c r="C377">
         <v>716</v>
@@ -34131,7 +34319,7 @@
         <v>376</v>
       </c>
       <c r="B378" t="s">
-        <v>378</v>
+        <v>405</v>
       </c>
       <c r="C378">
         <v>1105</v>
@@ -34217,7 +34405,7 @@
         <v>377</v>
       </c>
       <c r="B379" t="s">
-        <v>379</v>
+        <v>406</v>
       </c>
       <c r="C379">
         <v>681</v>
@@ -34303,7 +34491,7 @@
         <v>378</v>
       </c>
       <c r="B380" t="s">
-        <v>380</v>
+        <v>407</v>
       </c>
       <c r="C380">
         <v>588</v>
@@ -34389,7 +34577,7 @@
         <v>379</v>
       </c>
       <c r="B381" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="C381">
         <v>1125</v>
@@ -34475,7 +34663,7 @@
         <v>380</v>
       </c>
       <c r="B382" t="s">
-        <v>382</v>
+        <v>409</v>
       </c>
       <c r="C382">
         <v>1051</v>
@@ -34561,7 +34749,7 @@
         <v>381</v>
       </c>
       <c r="B383" t="s">
-        <v>383</v>
+        <v>410</v>
       </c>
       <c r="C383">
         <v>710</v>
@@ -34647,7 +34835,7 @@
         <v>382</v>
       </c>
       <c r="B384" t="s">
-        <v>384</v>
+        <v>411</v>
       </c>
       <c r="C384">
         <v>574</v>
@@ -34733,7 +34921,7 @@
         <v>383</v>
       </c>
       <c r="B385" t="s">
-        <v>385</v>
+        <v>412</v>
       </c>
       <c r="C385">
         <v>969</v>
@@ -34819,7 +35007,7 @@
         <v>384</v>
       </c>
       <c r="B386" t="s">
-        <v>386</v>
+        <v>413</v>
       </c>
       <c r="C386">
         <v>669</v>
@@ -34905,7 +35093,7 @@
         <v>385</v>
       </c>
       <c r="B387" t="s">
-        <v>387</v>
+        <v>414</v>
       </c>
       <c r="C387">
         <v>741</v>
@@ -34991,7 +35179,7 @@
         <v>386</v>
       </c>
       <c r="B388" t="s">
-        <v>388</v>
+        <v>415</v>
       </c>
       <c r="C388">
         <v>839</v>
@@ -35077,7 +35265,7 @@
         <v>387</v>
       </c>
       <c r="B389" t="s">
-        <v>389</v>
+        <v>416</v>
       </c>
       <c r="C389">
         <v>1079</v>
@@ -35163,7 +35351,7 @@
         <v>388</v>
       </c>
       <c r="B390" t="s">
-        <v>390</v>
+        <v>417</v>
       </c>
       <c r="C390">
         <v>1107</v>
@@ -35249,7 +35437,7 @@
         <v>389</v>
       </c>
       <c r="B391" t="s">
-        <v>391</v>
+        <v>418</v>
       </c>
       <c r="C391">
         <v>948</v>
@@ -35335,7 +35523,7 @@
         <v>390</v>
       </c>
       <c r="B392" t="s">
-        <v>392</v>
+        <v>419</v>
       </c>
       <c r="C392">
         <v>721</v>
@@ -35421,7 +35609,7 @@
         <v>391</v>
       </c>
       <c r="B393" t="s">
-        <v>393</v>
+        <v>420</v>
       </c>
       <c r="C393">
         <v>719</v>
@@ -35507,7 +35695,7 @@
         <v>392</v>
       </c>
       <c r="B394" t="s">
-        <v>394</v>
+        <v>421</v>
       </c>
       <c r="C394">
         <v>873</v>
@@ -35593,7 +35781,7 @@
         <v>393</v>
       </c>
       <c r="B395" t="s">
-        <v>395</v>
+        <v>422</v>
       </c>
       <c r="C395">
         <v>678</v>
@@ -35679,7 +35867,7 @@
         <v>394</v>
       </c>
       <c r="B396" t="s">
-        <v>396</v>
+        <v>423</v>
       </c>
       <c r="C396">
         <v>908</v>
@@ -35765,7 +35953,7 @@
         <v>395</v>
       </c>
       <c r="B397" t="s">
-        <v>397</v>
+        <v>424</v>
       </c>
       <c r="C397">
         <v>1005</v>
@@ -35851,7 +36039,7 @@
         <v>396</v>
       </c>
       <c r="B398" t="s">
-        <v>398</v>
+        <v>425</v>
       </c>
       <c r="C398">
         <v>928</v>
@@ -35937,7 +36125,7 @@
         <v>397</v>
       </c>
       <c r="B399" t="s">
-        <v>399</v>
+        <v>426</v>
       </c>
       <c r="C399">
         <v>644</v>
@@ -36023,7 +36211,7 @@
         <v>398</v>
       </c>
       <c r="B400" t="s">
-        <v>400</v>
+        <v>427</v>
       </c>
       <c r="C400">
         <v>1117</v>
@@ -36109,7 +36297,7 @@
         <v>399</v>
       </c>
       <c r="B401" t="s">
-        <v>401</v>
+        <v>428</v>
       </c>
       <c r="C401">
         <v>1015</v>
@@ -36195,7 +36383,7 @@
         <v>400</v>
       </c>
       <c r="B402" t="s">
-        <v>402</v>
+        <v>429</v>
       </c>
       <c r="C402">
         <v>939</v>
@@ -36281,7 +36469,7 @@
         <v>401</v>
       </c>
       <c r="B403" t="s">
-        <v>403</v>
+        <v>430</v>
       </c>
       <c r="C403">
         <v>1025</v>
@@ -36367,7 +36555,7 @@
         <v>402</v>
       </c>
       <c r="B404" t="s">
-        <v>404</v>
+        <v>431</v>
       </c>
       <c r="C404">
         <v>968</v>
@@ -36453,7 +36641,7 @@
         <v>403</v>
       </c>
       <c r="B405" t="s">
-        <v>405</v>
+        <v>432</v>
       </c>
       <c r="C405">
         <v>1062</v>
@@ -36539,7 +36727,7 @@
         <v>404</v>
       </c>
       <c r="B406" t="s">
-        <v>406</v>
+        <v>433</v>
       </c>
       <c r="C406">
         <v>796</v>
@@ -36625,7 +36813,7 @@
         <v>405</v>
       </c>
       <c r="B407" t="s">
-        <v>407</v>
+        <v>434</v>
       </c>
       <c r="C407">
         <v>946</v>
@@ -36711,7 +36899,7 @@
         <v>406</v>
       </c>
       <c r="B408" t="s">
-        <v>408</v>
+        <v>435</v>
       </c>
       <c r="C408">
         <v>1102</v>
@@ -36797,7 +36985,7 @@
         <v>407</v>
       </c>
       <c r="B409" t="s">
-        <v>409</v>
+        <v>436</v>
       </c>
       <c r="C409">
         <v>874</v>
@@ -36883,7 +37071,7 @@
         <v>408</v>
       </c>
       <c r="B410" t="s">
-        <v>410</v>
+        <v>437</v>
       </c>
       <c r="C410">
         <v>1127</v>
@@ -36969,7 +37157,7 @@
         <v>409</v>
       </c>
       <c r="B411" t="s">
-        <v>411</v>
+        <v>438</v>
       </c>
       <c r="C411">
         <v>748</v>
@@ -37055,7 +37243,7 @@
         <v>410</v>
       </c>
       <c r="B412" t="s">
-        <v>412</v>
+        <v>439</v>
       </c>
       <c r="C412">
         <v>792</v>
@@ -37141,7 +37329,7 @@
         <v>411</v>
       </c>
       <c r="B413" t="s">
-        <v>413</v>
+        <v>440</v>
       </c>
       <c r="C413">
         <v>834</v>
@@ -37227,7 +37415,7 @@
         <v>412</v>
       </c>
       <c r="B414" t="s">
-        <v>414</v>
+        <v>441</v>
       </c>
       <c r="C414">
         <v>722</v>
@@ -37313,7 +37501,7 @@
         <v>413</v>
       </c>
       <c r="B415" t="s">
-        <v>415</v>
+        <v>442</v>
       </c>
       <c r="C415">
         <v>742</v>
@@ -37399,7 +37587,7 @@
         <v>414</v>
       </c>
       <c r="B416" t="s">
-        <v>416</v>
+        <v>443</v>
       </c>
       <c r="C416">
         <v>999</v>
@@ -37485,7 +37673,7 @@
         <v>415</v>
       </c>
       <c r="B417" t="s">
-        <v>417</v>
+        <v>444</v>
       </c>
       <c r="C417">
         <v>1089</v>
@@ -37571,7 +37759,7 @@
         <v>416</v>
       </c>
       <c r="B418" t="s">
-        <v>418</v>
+        <v>445</v>
       </c>
       <c r="C418">
         <v>1129</v>
@@ -37657,7 +37845,7 @@
         <v>417</v>
       </c>
       <c r="B419" t="s">
-        <v>419</v>
+        <v>446</v>
       </c>
       <c r="C419">
         <v>1147</v>
@@ -37743,7 +37931,7 @@
         <v>418</v>
       </c>
       <c r="B420" t="s">
-        <v>420</v>
+        <v>447</v>
       </c>
       <c r="C420">
         <v>847</v>
@@ -37829,7 +38017,7 @@
         <v>419</v>
       </c>
       <c r="B421" t="s">
-        <v>421</v>
+        <v>448</v>
       </c>
       <c r="C421">
         <v>978</v>
@@ -37915,7 +38103,7 @@
         <v>420</v>
       </c>
       <c r="B422" t="s">
-        <v>422</v>
+        <v>449</v>
       </c>
       <c r="C422">
         <v>1147</v>
@@ -38001,7 +38189,7 @@
         <v>421</v>
       </c>
       <c r="B423" t="s">
-        <v>423</v>
+        <v>450</v>
       </c>
       <c r="C423">
         <v>626</v>
@@ -38087,7 +38275,7 @@
         <v>422</v>
       </c>
       <c r="B424" t="s">
-        <v>424</v>
+        <v>451</v>
       </c>
       <c r="C424">
         <v>623</v>
@@ -38173,7 +38361,7 @@
         <v>423</v>
       </c>
       <c r="B425" t="s">
-        <v>425</v>
+        <v>452</v>
       </c>
       <c r="C425">
         <v>1135</v>
@@ -38259,7 +38447,7 @@
         <v>424</v>
       </c>
       <c r="B426" t="s">
-        <v>426</v>
+        <v>453</v>
       </c>
       <c r="C426">
         <v>1136</v>
@@ -38345,7 +38533,7 @@
         <v>425</v>
       </c>
       <c r="B427" t="s">
-        <v>427</v>
+        <v>454</v>
       </c>
       <c r="C427">
         <v>738</v>
@@ -38431,7 +38619,7 @@
         <v>426</v>
       </c>
       <c r="B428" t="s">
-        <v>428</v>
+        <v>455</v>
       </c>
       <c r="C428">
         <v>683</v>
@@ -38517,7 +38705,7 @@
         <v>427</v>
       </c>
       <c r="B429" t="s">
-        <v>429</v>
+        <v>456</v>
       </c>
       <c r="C429">
         <v>983</v>
@@ -38603,7 +38791,7 @@
         <v>428</v>
       </c>
       <c r="B430" t="s">
-        <v>430</v>
+        <v>457</v>
       </c>
       <c r="C430">
         <v>1117</v>
@@ -38689,7 +38877,7 @@
         <v>429</v>
       </c>
       <c r="B431" t="s">
-        <v>431</v>
+        <v>458</v>
       </c>
       <c r="C431">
         <v>1097</v>
@@ -38775,7 +38963,7 @@
         <v>430</v>
       </c>
       <c r="B432" t="s">
-        <v>432</v>
+        <v>459</v>
       </c>
       <c r="C432">
         <v>747</v>
@@ -38861,7 +39049,7 @@
         <v>431</v>
       </c>
       <c r="B433" t="s">
-        <v>433</v>
+        <v>460</v>
       </c>
       <c r="C433">
         <v>916</v>
@@ -38947,7 +39135,7 @@
         <v>432</v>
       </c>
       <c r="B434" t="s">
-        <v>434</v>
+        <v>461</v>
       </c>
       <c r="C434">
         <v>711</v>
@@ -39033,7 +39221,7 @@
         <v>433</v>
       </c>
       <c r="B435" t="s">
-        <v>435</v>
+        <v>462</v>
       </c>
       <c r="C435">
         <v>643</v>
@@ -39119,7 +39307,7 @@
         <v>434</v>
       </c>
       <c r="B436" t="s">
-        <v>436</v>
+        <v>463</v>
       </c>
       <c r="C436">
         <v>595</v>
@@ -39205,7 +39393,7 @@
         <v>435</v>
       </c>
       <c r="B437" t="s">
-        <v>437</v>
+        <v>464</v>
       </c>
       <c r="C437">
         <v>1075</v>
@@ -39291,7 +39479,7 @@
         <v>436</v>
       </c>
       <c r="B438" t="s">
-        <v>438</v>
+        <v>465</v>
       </c>
       <c r="C438">
         <v>843</v>
@@ -39377,7 +39565,7 @@
         <v>437</v>
       </c>
       <c r="B439" t="s">
-        <v>439</v>
+        <v>466</v>
       </c>
       <c r="C439">
         <v>672</v>
@@ -39463,7 +39651,7 @@
         <v>438</v>
       </c>
       <c r="B440" t="s">
-        <v>440</v>
+        <v>467</v>
       </c>
       <c r="C440">
         <v>1103</v>
@@ -39549,7 +39737,7 @@
         <v>439</v>
       </c>
       <c r="B441" t="s">
-        <v>441</v>
+        <v>468</v>
       </c>
       <c r="C441">
         <v>817</v>
@@ -39635,7 +39823,7 @@
         <v>440</v>
       </c>
       <c r="B442" t="s">
-        <v>442</v>
+        <v>469</v>
       </c>
       <c r="C442">
         <v>1045</v>
@@ -39721,7 +39909,7 @@
         <v>441</v>
       </c>
       <c r="B443" t="s">
-        <v>443</v>
+        <v>470</v>
       </c>
       <c r="C443">
         <v>870</v>
@@ -39807,7 +39995,7 @@
         <v>442</v>
       </c>
       <c r="B444" t="s">
-        <v>444</v>
+        <v>471</v>
       </c>
       <c r="C444">
         <v>649</v>
@@ -39893,7 +40081,7 @@
         <v>443</v>
       </c>
       <c r="B445" t="s">
-        <v>445</v>
+        <v>472</v>
       </c>
       <c r="C445">
         <v>714</v>
@@ -39979,7 +40167,7 @@
         <v>444</v>
       </c>
       <c r="B446" t="s">
-        <v>446</v>
+        <v>473</v>
       </c>
       <c r="C446">
         <v>823</v>
@@ -40065,7 +40253,7 @@
         <v>445</v>
       </c>
       <c r="B447" t="s">
-        <v>447</v>
+        <v>474</v>
       </c>
       <c r="C447">
         <v>862</v>
@@ -40151,7 +40339,7 @@
         <v>446</v>
       </c>
       <c r="B448" t="s">
-        <v>448</v>
+        <v>475</v>
       </c>
       <c r="C448">
         <v>1004</v>
@@ -40237,7 +40425,7 @@
         <v>447</v>
       </c>
       <c r="B449" t="s">
-        <v>449</v>
+        <v>476</v>
       </c>
       <c r="C449">
         <v>1000</v>
@@ -40323,7 +40511,7 @@
         <v>448</v>
       </c>
       <c r="B450" t="s">
-        <v>450</v>
+        <v>477</v>
       </c>
       <c r="C450">
         <v>1153</v>
@@ -40409,7 +40597,7 @@
         <v>449</v>
       </c>
       <c r="B451" t="s">
-        <v>451</v>
+        <v>478</v>
       </c>
       <c r="C451">
         <v>1040</v>
@@ -40495,7 +40683,7 @@
         <v>450</v>
       </c>
       <c r="B452" t="s">
-        <v>452</v>
+        <v>479</v>
       </c>
       <c r="C452">
         <v>1137</v>
@@ -40581,7 +40769,7 @@
         <v>451</v>
       </c>
       <c r="B453" t="s">
-        <v>453</v>
+        <v>480</v>
       </c>
       <c r="C453">
         <v>930</v>
